--- a/AI_AuditLog_SWR302.xlsx
+++ b/AI_AuditLog_SWR302.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\5_SEMESTER\SWR302\ai-audit-log-bloan-7105\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257F354C-FE76-4070-BA63-8920BC0C02BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71C18E73-C50A-4EBD-9D6B-03E851835437}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Metadata &amp; Summary" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="174">
   <si>
     <t>AI AUDIT LOG - METADATA &amp; SUMMARY</t>
   </si>
@@ -114,18 +114,6 @@
     <t>Deep reflection</t>
   </si>
   <si>
-    <t>GitHub Copilot</t>
-  </si>
-  <si>
-    <t>Auto-completion</t>
-  </si>
-  <si>
-    <t>Speed up coding</t>
-  </si>
-  <si>
-    <t>[Add more...]</t>
-  </si>
-  <si>
     <t>CORE PROMPTS DISTRIBUTION BY DTC COMPONENT</t>
   </si>
   <si>
@@ -186,21 +174,12 @@
     <t>001</t>
   </si>
   <si>
-    <t>DECISION</t>
-  </si>
-  <si>
     <t>002</t>
   </si>
   <si>
-    <t>PROBLEM-SOLVING</t>
-  </si>
-  <si>
     <t>003</t>
   </si>
   <si>
-    <t>VERIFICATION</t>
-  </si>
-  <si>
     <t>HALLUCINATION DETECTION LOG (BẮT BUỘC)</t>
   </si>
   <si>
@@ -387,337 +366,196 @@
     <t>SWR302</t>
   </si>
   <si>
-    <t>HRP</t>
-  </si>
-  <si>
     <t>Requirement Analysis</t>
   </si>
   <si>
-    <t>Requirement trong đề dài và khó xác định actor</t>
-  </si>
-  <si>
-    <t>"Phân tích đề bài và xác định actor chính, actor phụ"</t>
-  </si>
-  <si>
-    <t>AI đề xuất Customer, Staff, Admin</t>
-  </si>
-  <si>
-    <t>Critical Thinking: AI xem Staff là actor riêng nhưng đề không mô tả rõ quyền hạn. Contextualization: Đề chỉ yêu cầu quản lý bởi Admin. Creative Synthesis: Gộp Staff vào Admin. Decision: Chọn 2 actor chính là Customer và Admin.</t>
-  </si>
-  <si>
-    <t>Requirement analysis notes</t>
-  </si>
-  <si>
-    <t>Context Diagram</t>
-  </si>
-  <si>
-    <t>Khó xác định luồng dữ liệu vào/ra hệ thống</t>
-  </si>
-  <si>
-    <t>"Liệt kê các data flow cho context diagram"</t>
-  </si>
-  <si>
-    <t>AI đề xuất Input: Registration, Booking Request; Output: Confirmation, Reports</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Một số flow bị trùng nhau. Contextualization: Theo scope môn SWR chỉ mô tả mức tổng quát. Creative Synthesis: Gộp các flow thành 6 luồng chính. Decision: Sử dụng phiên bản rút gọn cho Context Diagram.</t>
-  </si>
-  <si>
-    <t>Context Diagram v1/v2</t>
-  </si>
-  <si>
-    <t>Use Case Modeling</t>
-  </si>
-  <si>
-    <t>Chưa biết chia use case như thế nào</t>
-  </si>
-  <si>
-    <t>"Tạo danh sách use case từ requirement"</t>
-  </si>
-  <si>
-    <t>AI đề xuất 12 use case</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Có use case quá chi tiết. Contextualization: Use Case Diagram nên thể hiện chức năng nghiệp vụ chính. Creative Synthesis: Giảm còn 8 use case. Decision: Chọn 8 use case để tránh diagram quá phức tạp.</t>
-  </si>
-  <si>
-    <t>Use Case Diagram</t>
-  </si>
-  <si>
-    <t>Swimlane Diagram</t>
-  </si>
-  <si>
-    <t>Khó xác định activity và decision</t>
-  </si>
-  <si>
-    <t>"Phân tích quy trình booking và các decision point"</t>
-  </si>
-  <si>
-    <t>AI đưa các bước booking và xác nhận</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Thiếu bước validate thông tin. Contextualization: Requirement yêu cầu kiểm tra dữ liệu trước khi lưu. Creative Synthesis: Thêm activity Validate Information và decision Valid/Invalid. Decision: Cập nhật Swimlane Diagram.</t>
-  </si>
-  <si>
-    <t>Swimlane v2</t>
-  </si>
-  <si>
-    <t>Functional Requirements</t>
-  </si>
-  <si>
-    <t>Muốn kiểm tra FR đã đầy đủ chưa</t>
-  </si>
-  <si>
-    <t>"Review danh sách Functional Requirements"</t>
-  </si>
-  <si>
-    <t>AI phát hiện thiếu chức năng cập nhật thông tin</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Kiểm tra lại đề thấy requirement này thực sự tồn tại. Contextualization: Đây là chức năng bắt buộc. Creative Synthesis: Bổ sung FR-07 Update Information. Decision: Cập nhật SRS.</t>
-  </si>
-  <si>
-    <t>SRS revision</t>
-  </si>
-  <si>
-    <t>Non-functional Requirements</t>
-  </si>
-  <si>
-    <t>Chưa xác định NFR phù hợp</t>
-  </si>
-  <si>
-    <t>"Đề xuất Non-functional Requirements cho hệ thống"</t>
-  </si>
-  <si>
-    <t>AI đề xuất Security, Performance, Availability</t>
-  </si>
-  <si>
-    <t>Critical Thinking: AI đề xuất Availability 99.99% không phù hợp bài môn học. Contextualization: Đây không phải hệ thống production. Creative Synthesis: Giảm xuống các NFR cơ bản. Decision: Chọn Security, Performance, Usability.</t>
-  </si>
-  <si>
-    <t>SRS NFR section</t>
-  </si>
-  <si>
     <t>Scope Expansion</t>
   </si>
   <si>
-    <t>Use Case Description</t>
-  </si>
-  <si>
-    <t>Chưa biết viết Main Flow và Alternative Flow</t>
-  </si>
-  <si>
-    <t>"Viết Use Case Description cho chức năng đặt dịch vụ"</t>
-  </si>
-  <si>
-    <t>AI đề xuất các bước thực hiện và luồng thay thế</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Một số bước không xuất hiện trong đề bài. Contextualization: Chỉ giữ các bước có trong requirement. Creative Synthesis: Điều chỉnh lại luồng xử lý. Decision: Hoàn thiện Use Case Description theo đề.</t>
-  </si>
-  <si>
-    <t>Muốn kiểm tra requirement đã đầy đủ chưa</t>
-  </si>
-  <si>
-    <t>AI đề xuất thêm một số chức năng</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Có chức năng ngoài phạm vi đề bài. Contextualization: So sánh lại với yêu cầu hệ thống. Creative Synthesis: Chỉ bổ sung các requirement còn thiếu. Decision: Cập nhật danh sách FR.</t>
-  </si>
-  <si>
-    <t>Requirement List</t>
-  </si>
-  <si>
-    <t>Chưa chắc actor nào được phép thực hiện chức năng</t>
-  </si>
-  <si>
-    <t>"Xác định actor cho từng use case"</t>
-  </si>
-  <si>
-    <t>AI gán actor cho các chức năng chính</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Một số use case được gán cho nhiều actor không hợp lý. Contextualization: Dựa trên mô tả nghiệp vụ. Creative Synthesis: Điều chỉnh lại quan hệ actor-use case. Decision: Cập nhật Use Case Diagram.</t>
-  </si>
-  <si>
-    <t>Use Case Diagram v2</t>
-  </si>
-  <si>
-    <t>Activity Diagram</t>
-  </si>
-  <si>
-    <t>Khó xác định các decision node</t>
-  </si>
-  <si>
-    <t>"Phân tích quy trình và xác định decision points"</t>
-  </si>
-  <si>
-    <t>AI đề xuất các điều kiện rẽ nhánh</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Một số decision không ảnh hưởng đến luồng nghiệp vụ. Contextualization: Chỉ giữ các điều kiện quan trọng. Creative Synthesis: Rút gọn Activity Diagram. Decision: Hoàn thiện sơ đồ cuối cùng.</t>
-  </si>
-  <si>
-    <t>State Diagram</t>
-  </si>
-  <si>
-    <t>Chưa biết xác định trạng thái của đối tượng</t>
-  </si>
-  <si>
-    <t>"Xác định các state và transition cho đối tượng Booking"</t>
-  </si>
-  <si>
-    <t>AI đề xuất các trạng thái Created, Pending, Approved, Cancelled</t>
-  </si>
-  <si>
-    <t>Critical Thinking: Có trạng thái không được đề cập trong requirement. Contextualization: Kiểm tra lại luồng nghiệp vụ. Creative Synthesis: Giữ lại các state thực sự tồn tại. Decision: Hoàn thành State Diagram.</t>
-  </si>
-  <si>
-    <t>AI đề xuất thêm chức năng thanh toán trực tuyến</t>
-  </si>
-  <si>
-    <t>Đề bài không đề cập chức năng thanh toán</t>
-  </si>
-  <si>
-    <t>Đối chiếu Requirement Specification</t>
-  </si>
-  <si>
-    <t>Loại bỏ chức năng khỏi Use Case Diagram</t>
-  </si>
-  <si>
-    <t>Incorrect Actor Assignment</t>
-  </si>
-  <si>
-    <t>AI gán Customer thực hiện chức năng quản trị hệ thống</t>
-  </si>
-  <si>
-    <t>Chức năng này chỉ dành cho Admin</t>
-  </si>
-  <si>
-    <t>So sánh với mô tả actor trong đề</t>
-  </si>
-  <si>
-    <t>Chỉnh lại quan hệ Actor-Use Case</t>
-  </si>
-  <si>
-    <t>Missing Business Rule</t>
-  </si>
-  <si>
-    <t>AI bỏ qua bước kiểm tra dữ liệu đầu vào</t>
-  </si>
-  <si>
-    <t>Requirement yêu cầu hệ thống xác thực dữ liệu</t>
-  </si>
-  <si>
-    <t>Kiểm tra lại đề bài và Activity Diagram</t>
-  </si>
-  <si>
-    <t>Bổ sung bước Validate Information</t>
-  </si>
-  <si>
-    <t>Invalid State</t>
-  </si>
-  <si>
-    <t>AI thêm trạng thái "Archived" trong State Diagram</t>
-  </si>
-  <si>
-    <t>Trạng thái này không tồn tại trong nghiệp vụ</t>
-  </si>
-  <si>
-    <t>Đối chiếu luồng xử lý của hệ thống</t>
-  </si>
-  <si>
-    <t>Xóa trạng thái khỏi State Diagram</t>
-  </si>
-  <si>
-    <t>Over-Generalization</t>
-  </si>
-  <si>
-    <t>AI đề xuất quá nhiều Non-functional Requirements</t>
-  </si>
-  <si>
-    <t>Đề bài chỉ yêu cầu mô tả chức năng chính</t>
-  </si>
-  <si>
-    <t>So sánh với phạm vi môn học</t>
-  </si>
-  <si>
-    <t>Chỉ giữ các NFR cơ bản</t>
-  </si>
-  <si>
-    <t>Missing Alternative Flow</t>
-  </si>
-  <si>
-    <t>AI chỉ tạo Main Flow cho Use Case</t>
-  </si>
-  <si>
-    <t>Use Case cần có cả Alternative Flow</t>
-  </si>
-  <si>
-    <t>Review Use Case Description</t>
-  </si>
-  <si>
-    <t>Bổ sung luồng thay thế</t>
-  </si>
-  <si>
-    <t>Diagram Inconsistency</t>
-  </si>
-  <si>
-    <t>AI tạo Use Case không xuất hiện trong Requirement List</t>
-  </si>
-  <si>
-    <t>Requirement không mô tả chức năng đó</t>
-  </si>
-  <si>
-    <t>Cross-check giữa Requirement và Diagram</t>
-  </si>
-  <si>
-    <t>Loại bỏ Use Case</t>
-  </si>
-  <si>
-    <t>Incorrect Data Flow</t>
-  </si>
-  <si>
-    <t>AI tạo luồng dữ liệu không đi qua hệ thống trong Context Diagram</t>
-  </si>
-  <si>
-    <t>Context Diagram chỉ mô tả tương tác với hệ thống</t>
-  </si>
-  <si>
-    <t>Review theo quy tắc Context Diagram</t>
-  </si>
-  <si>
-    <t>Chỉnh lại Data Flow</t>
-  </si>
-  <si>
-    <t>Ambiguous Requirement Interpretation</t>
-  </si>
-  <si>
-    <t>AI hiểu "quản lý thông tin" thành nhiều chức năng riêng biệt</t>
-  </si>
-  <si>
-    <t>Đề bài mô tả đây là một chức năng tổng quát</t>
-  </si>
-  <si>
-    <t>Đối chiếu wording trong đề</t>
-  </si>
-  <si>
-    <t>Gom các chức năng thành một Use Case</t>
-  </si>
-  <si>
-    <t>Unsupported Assumption</t>
-  </si>
-  <si>
-    <t>AI giả định hệ thống có gửi email tự động</t>
-  </si>
-  <si>
-    <t>Requirement không nhắc đến email notification</t>
-  </si>
-  <si>
-    <t>Kiểm tra toàn bộ đề bài</t>
-  </si>
-  <si>
-    <t>✓</t>
+    <t>Chapter 16-17 Individual Assignment</t>
+  </si>
+  <si>
+    <t>Exercise 1a</t>
+  </si>
+  <si>
+    <t>Exercise 1b</t>
+  </si>
+  <si>
+    <t>Requirement Prioritization</t>
+  </si>
+  <si>
+    <t>Decision</t>
+  </si>
+  <si>
+    <t>Khó xác định mức ưu tiên của 10 requirements</t>
+  </si>
+  <si>
+    <t>Phân loại các requirement theo mô hình MoSCoW cho hệ thống đặt lịch khám bệnh</t>
+  </si>
+  <si>
+    <t>AI đề xuất phân loại Must/Should/Could/Won't</t>
+  </si>
+  <si>
+    <t>Đánh giá lại theo bối cảnh dự án 8 tuần, 3 developers và mục tiêu MVP; giữ lại các chức năng trực tiếp phục vụ đặt lịch</t>
+  </si>
+  <si>
+    <t>Chưa xác định được lý do cho các Must Have</t>
+  </si>
+  <si>
+    <t>Nếu bỏ từng Must Have thì hệ thống có còn đáp ứng mục tiêu chính không?</t>
+  </si>
+  <si>
+    <t>AI giải thích business impact của từng requirement</t>
+  </si>
+  <si>
+    <t>Chỉnh sửa lập luận để phù hợp với quy trình khám bệnh và đặc thù phòng khám</t>
+  </si>
+  <si>
+    <t>Requirement Validation</t>
+  </si>
+  <si>
+    <t>Problem-Solving</t>
+  </si>
+  <si>
+    <t>Khó xây dựng câu hỏi Games People Play</t>
+  </si>
+  <si>
+    <t>Viết câu hỏi BA dùng để kiểm tra requirement có thực sự cần thiết không</t>
+  </si>
+  <si>
+    <t>AI đưa ra các câu hỏi về giá trị, chi phí và giải pháp thay thế</t>
+  </si>
+  <si>
+    <t>Chọn lọc và điều chỉnh câu hỏi cho SMS reminder và báo cáo doanh thu</t>
+  </si>
+  <si>
+    <t>Verification &amp; Validation</t>
+  </si>
+  <si>
+    <t>Khó phân biệt Verification và Validation trong các tình huống</t>
+  </si>
+  <si>
+    <t>Phân loại các tình huống TH1–TH5</t>
+  </si>
+  <si>
+    <t>AI giải thích từng tình huống</t>
+  </si>
+  <si>
+    <t>Đối chiếu lại với lý thuyết chương 17 và điều chỉnh cho phù hợp với ngữ cảnh bài tập</t>
+  </si>
+  <si>
+    <t>Exercise 2a</t>
+  </si>
+  <si>
+    <t>Root Cause Analysis</t>
+  </si>
+  <si>
+    <t>Verification</t>
+  </si>
+  <si>
+    <t>Muốn phân tích sâu TH5</t>
+  </si>
+  <si>
+    <t>Vì sao tất cả test PASS nhưng khách hàng vẫn từ chối nghiệm thu?</t>
+  </si>
+  <si>
+    <t>AI giải thích sự khác biệt giữa Verification và Validation</t>
+  </si>
+  <si>
+    <t>Bổ sung ví dụ thực tế và liên hệ với quy trình BA</t>
+  </si>
+  <si>
+    <t>Exercise 2b</t>
+  </si>
+  <si>
+    <t>Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Chưa biết viết Acceptance Criteria theo Given-When-Then</t>
+  </si>
+  <si>
+    <t>Viết Acceptance Criteria cho user story đặt lịch khám</t>
+  </si>
+  <si>
+    <t>AI đề xuất nhiều Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>Chọn các AC phù hợp với user story và bổ sung các trường hợp ngoại lệ</t>
+  </si>
+  <si>
+    <t>Exercise 3a</t>
+  </si>
+  <si>
+    <t>Test Case Design</t>
+  </si>
+  <si>
+    <t>Kiểm tra test case đã đầy đủ chưa</t>
+  </si>
+  <si>
+    <t>Review test case dựa trên Acceptance Criteria</t>
+  </si>
+  <si>
+    <t>AI đề xuất cấu trúc test case đầy đủ</t>
+  </si>
+  <si>
+    <t>Điều chỉnh dữ liệu kiểm thử và kết quả mong đợi theo ngữ cảnh bài tập</t>
+  </si>
+  <si>
+    <t>Exercise 3c</t>
+  </si>
+  <si>
+    <t>H01</t>
+  </si>
+  <si>
+    <t>R06 (Đặt lịch tại 3 cơ sở) phải là Must Have</t>
+  </si>
+  <si>
+    <t>Priority Misclassification</t>
+  </si>
+  <si>
+    <t>Đối chiếu với phạm vi MVP và nguồn lực dự án</t>
+  </si>
+  <si>
+    <t>Xem xét lại mức độ ưu tiên theo deadline và nguồn lực</t>
+  </si>
+  <si>
+    <t>Giữ ở mức thấp hơn (Could/Should/Won't tùy lập luận)</t>
+  </si>
+  <si>
+    <t>H02</t>
+  </si>
+  <si>
+    <t>Acceptance Criteria nên bao gồm nhiều chức năng ngoài user story</t>
+  </si>
+  <si>
+    <t>So sánh với user story gốc chỉ tập trung vào đặt lịch</t>
+  </si>
+  <si>
+    <t>Loại bỏ các AC không phục vụ trực tiếp user story</t>
+  </si>
+  <si>
+    <t>Giữ lại AC liên quan trực tiếp đến đặt lịch</t>
+  </si>
+  <si>
+    <t>H03</t>
+  </si>
+  <si>
+    <t>TH5 chỉ thuộc Verification</t>
+  </si>
+  <si>
+    <t>Concept Misclassification</t>
+  </si>
+  <si>
+    <t>Đối chiếu định nghĩa Verification và Validation trong chương 17</t>
+  </si>
+  <si>
+    <t>Phân tích lại nguyên nhân dự án bị từ chối</t>
+  </si>
+  <si>
+    <t>Xác định TH5 liên quan đến cả Verification và Validation</t>
+  </si>
+  <si>
+    <t>☑</t>
   </si>
 </sst>
 </file>
@@ -727,7 +565,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -809,6 +647,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -863,7 +707,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -900,10 +744,19 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -913,14 +766,11 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1224,25 +1074,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
     <col min="2" max="2" width="40" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
+    <col min="3" max="3" width="18.5546875" customWidth="1"/>
     <col min="4" max="4" width="30" customWidth="1"/>
     <col min="5" max="6" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
@@ -1254,7 +1104,7 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1262,7 +1112,7 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
@@ -1270,15 +1120,15 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" t="s">
-        <v>117</v>
+      <c r="C7" s="18" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
@@ -1290,20 +1140,25 @@
       <c r="A10" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3"/>
+      <c r="C11" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="4" t="e">
+      <c r="C12" s="4">
         <f>C11/C10</f>
-        <v>#DIV/0!</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>10</v>
@@ -1364,86 +1219,64 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A19" s="7" t="s">
+    <row r="20" spans="1:4" ht="18" x14ac:dyDescent="0.35">
+      <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="7" t="s">
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D19" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A20" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-    </row>
-    <row r="22" spans="1:4" ht="18" x14ac:dyDescent="0.35">
-      <c r="A22" s="1" t="s">
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A22" s="7" t="s">
         <v>30</v>
       </c>
+      <c r="B22" s="8">
+        <v>0</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="8">
+        <v>0</v>
+      </c>
+      <c r="C23" s="9" t="s">
         <v>31</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="8">
         <v>0</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B25" s="8">
         <v>0</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A26" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="B26" s="8">
-        <v>0</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A27" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="B27" s="8">
-        <v>0</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1469,340 +1302,276 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>39</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
     </row>
     <row r="2" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>40</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="A2" s="23" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
     </row>
     <row r="3" spans="1:8" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>48</v>
-      </c>
     </row>
     <row r="4" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
+      <c r="A4" s="19">
         <v>1</v>
       </c>
-      <c r="B4" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C4" s="24" t="s">
+      <c r="B4" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="18" t="s">
         <v>118</v>
       </c>
-      <c r="D4" s="24" t="s">
+      <c r="F4" s="18" t="s">
         <v>119</v>
       </c>
-      <c r="E4" s="24" t="s">
+      <c r="G4" s="18" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="24" t="s">
+      <c r="H4" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="19">
+        <v>2</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="G4" s="24" t="s">
+      <c r="E5" s="18" t="s">
         <v>122</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="F5" s="18" t="s">
         <v>123</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
-        <v>2</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="24" t="s">
+      <c r="G5" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="D5" s="24" t="s">
+      <c r="H5" s="18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="19">
+        <v>3</v>
+      </c>
+      <c r="B6" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="C6" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F5" s="24" t="s">
+      <c r="D6" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="G5" s="24" t="s">
+      <c r="E6" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="H5" s="24" t="s">
+      <c r="F6" s="18" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="100.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
-        <v>3</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="24" t="s">
+      <c r="G6" s="18" t="s">
         <v>130</v>
       </c>
-      <c r="D6" s="24" t="s">
+      <c r="H6" s="18" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="19">
+        <v>4</v>
+      </c>
+      <c r="B7" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="C7" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="F6" s="24" t="s">
+      <c r="E7" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="G6" s="24" t="s">
+      <c r="F7" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="H6" s="24" t="s">
+      <c r="G7" s="18" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
-        <v>4</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="24" t="s">
+      <c r="H7" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="24" t="s">
+    </row>
+    <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="19">
+        <v>5</v>
+      </c>
+      <c r="B8" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="C8" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="F7" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="G7" s="24" t="s">
+      <c r="E8" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="H7" s="24" t="s">
+      <c r="F8" s="18" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
-        <v>5</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="G8" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="D8" s="24" t="s">
+      <c r="H8" s="18" t="s">
         <v>143</v>
       </c>
-      <c r="E8" s="24" t="s">
+    </row>
+    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="19">
+        <v>6</v>
+      </c>
+      <c r="B9" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="F8" s="24" t="s">
+      <c r="C9" s="18" t="s">
+        <v>126</v>
+      </c>
+      <c r="D9" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="G8" s="24" t="s">
+      <c r="E9" s="18" t="s">
         <v>146</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="F9" s="18" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
-        <v>6</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C9" s="24" t="s">
+      <c r="G9" s="18" t="s">
         <v>148</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="H9" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="E9" s="24" t="s">
+    </row>
+    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19">
+        <v>7</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>150</v>
       </c>
-      <c r="F9" s="24" t="s">
+      <c r="C10" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="D10" s="18" t="s">
         <v>151</v>
       </c>
-      <c r="G9" s="24" t="s">
+      <c r="E10" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="H9" s="24" t="s">
+      <c r="F10" s="18" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
-        <v>7</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C10" s="24" t="s">
+      <c r="G10" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="H10" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D10" s="24" t="s">
-        <v>156</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>157</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>158</v>
-      </c>
-      <c r="G10" s="24" t="s">
-        <v>159</v>
-      </c>
-      <c r="H10" s="24" t="s">
-        <v>155</v>
-      </c>
     </row>
     <row r="11" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
-        <v>8</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>144</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>161</v>
-      </c>
-      <c r="G11" s="24" t="s">
-        <v>162</v>
-      </c>
-      <c r="H11" s="24" t="s">
-        <v>163</v>
-      </c>
+      <c r="A11" s="19"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
-        <v>9</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>164</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>165</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>166</v>
-      </c>
-      <c r="G12" s="24" t="s">
-        <v>167</v>
-      </c>
-      <c r="H12" s="24" t="s">
-        <v>168</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
     </row>
     <row r="13" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
-        <v>10</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>169</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>170</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>171</v>
-      </c>
-      <c r="F13" s="24" t="s">
-        <v>172</v>
-      </c>
-      <c r="G13" s="24" t="s">
-        <v>173</v>
-      </c>
-      <c r="H13" s="24" t="s">
-        <v>169</v>
-      </c>
+      <c r="A13" s="19"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
     </row>
     <row r="14" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="25">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" s="24" t="s">
-        <v>174</v>
-      </c>
-      <c r="D14" s="24" t="s">
-        <v>175</v>
-      </c>
-      <c r="E14" s="24" t="s">
-        <v>176</v>
-      </c>
-      <c r="F14" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="G14" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="H14" s="24" t="s">
-        <v>174</v>
-      </c>
+      <c r="A14" s="19"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
     </row>
     <row r="15" spans="1:8" ht="79.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7"/>
@@ -1945,241 +1714,159 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
+      <c r="A1" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
+      <c r="A2" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
     </row>
     <row r="3" spans="1:6" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25">
-        <v>1</v>
-      </c>
-      <c r="B4" s="24" t="s">
-        <v>154</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>180</v>
-      </c>
-      <c r="E4" s="24" t="s">
-        <v>181</v>
-      </c>
-      <c r="F4" s="24" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="25">
-        <v>2</v>
-      </c>
-      <c r="B5" s="24" t="s">
-        <v>183</v>
-      </c>
-      <c r="C5" s="24" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="24" t="s">
-        <v>185</v>
-      </c>
-      <c r="E5" s="24" t="s">
-        <v>186</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>187</v>
+      <c r="A4" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>159</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>160</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>163</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>111</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>164</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>165</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25">
-        <v>3</v>
-      </c>
-      <c r="B6" s="24" t="s">
-        <v>188</v>
-      </c>
-      <c r="C6" s="24" t="s">
-        <v>189</v>
-      </c>
-      <c r="D6" s="24" t="s">
-        <v>190</v>
-      </c>
-      <c r="E6" s="24" t="s">
-        <v>191</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>192</v>
+      <c r="A6" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>168</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>169</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>171</v>
+      </c>
+      <c r="F6" s="18" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25">
-        <v>4</v>
-      </c>
-      <c r="B7" s="24" t="s">
-        <v>193</v>
-      </c>
-      <c r="C7" s="24" t="s">
-        <v>194</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>195</v>
-      </c>
-      <c r="E7" s="24" t="s">
-        <v>196</v>
-      </c>
-      <c r="F7" s="24" t="s">
-        <v>197</v>
-      </c>
+      <c r="A7" s="19"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25">
-        <v>5</v>
-      </c>
-      <c r="B8" s="24" t="s">
-        <v>198</v>
-      </c>
-      <c r="C8" s="24" t="s">
-        <v>199</v>
-      </c>
-      <c r="D8" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="E8" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>202</v>
-      </c>
+      <c r="A8" s="19"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="25">
-        <v>6</v>
-      </c>
-      <c r="B9" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="C9" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="D9" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="E9" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="F9" s="24" t="s">
-        <v>207</v>
-      </c>
+      <c r="A9" s="19"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
     </row>
     <row r="10" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="25">
-        <v>7</v>
-      </c>
-      <c r="B10" s="24" t="s">
-        <v>208</v>
-      </c>
-      <c r="C10" s="24" t="s">
-        <v>209</v>
-      </c>
-      <c r="D10" s="24" t="s">
-        <v>210</v>
-      </c>
-      <c r="E10" s="24" t="s">
-        <v>211</v>
-      </c>
-      <c r="F10" s="24" t="s">
-        <v>212</v>
-      </c>
+      <c r="A10" s="19"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="25">
-        <v>8</v>
-      </c>
-      <c r="B11" s="24" t="s">
-        <v>213</v>
-      </c>
-      <c r="C11" s="24" t="s">
-        <v>214</v>
-      </c>
-      <c r="D11" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="E11" s="24" t="s">
-        <v>216</v>
-      </c>
-      <c r="F11" s="24" t="s">
-        <v>217</v>
-      </c>
+      <c r="A11" s="19"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="25">
-        <v>9</v>
-      </c>
-      <c r="B12" s="24" t="s">
-        <v>218</v>
-      </c>
-      <c r="C12" s="24" t="s">
-        <v>219</v>
-      </c>
-      <c r="D12" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="E12" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="F12" s="24" t="s">
-        <v>222</v>
-      </c>
+      <c r="A12" s="19"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="25">
-        <v>10</v>
-      </c>
-      <c r="B13" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="C13" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="D13" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="E13" s="24" t="s">
-        <v>226</v>
-      </c>
+      <c r="A13" s="19"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
     </row>
     <row r="14" spans="1:6" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7"/>
@@ -2271,73 +1958,73 @@
     </row>
     <row r="30" spans="1:6" ht="18" x14ac:dyDescent="0.35">
       <c r="A30" s="1" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="7" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A36" s="7" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
   </sheetData>
@@ -2361,221 +2048,225 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
+      <c r="A1" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
+      <c r="A2" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
     </row>
     <row r="4" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A6" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D6" s="13"/>
+    </row>
+    <row r="7" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A7" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B5" s="11" t="s">
+      <c r="C7" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D7" s="13"/>
+    </row>
+    <row r="8" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A8" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="B8" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="C8" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D8" s="13"/>
+    </row>
+    <row r="9" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A9" s="12" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="C9" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="13"/>
+    </row>
+    <row r="10" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A10" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="B10" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>227</v>
+      <c r="C10" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="D10" s="13"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="C11" s="27"/>
     </row>
     <row r="12" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
-        <v>99</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="C12" s="27"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="B13" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A14" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="13"/>
+    </row>
+    <row r="15" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A15" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="D15" s="13"/>
+    </row>
+    <row r="16" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="A16" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>227</v>
-      </c>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>93</v>
-      </c>
       <c r="B16" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>227</v>
+        <v>96</v>
+      </c>
+      <c r="C16" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="D16" s="13"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A17" s="12" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="B17" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>227</v>
+        <v>97</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="D17" s="13"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="16.8" x14ac:dyDescent="0.4">
       <c r="A18" s="12" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>227</v>
+        <v>98</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>173</v>
       </c>
       <c r="D18" s="13"/>
     </row>
     <row r="20" spans="1:4" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A20" s="14" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="15" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="15" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="18" x14ac:dyDescent="0.35">
       <c r="A25" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A27" s="17" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B28" s="7"/>
       <c r="C28" s="7"/>
@@ -2583,7 +2274,7 @@
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -2591,7 +2282,7 @@
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
